--- a/data/final/bootstrap_summary_treatment.xlsx
+++ b/data/final/bootstrap_summary_treatment.xlsx
@@ -492,19 +492,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2172643.7555839</v>
+        <v>2173105.9151329</v>
       </c>
       <c r="E2" t="n">
-        <v>2172689.434</v>
+        <v>2172491.1705</v>
       </c>
       <c r="F2" t="n">
-        <v>2028157.067925</v>
+        <v>2027142.9985</v>
       </c>
       <c r="G2" t="n">
-        <v>2319299.49315</v>
+        <v>2330312.874225</v>
       </c>
       <c r="H2" t="n">
-        <v>75531.93020084548</v>
+        <v>76658.13864852587</v>
       </c>
       <c r="I2" t="n">
         <v>10000</v>
@@ -527,19 +527,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2409384.60857335</v>
+        <v>2410028.567033403</v>
       </c>
       <c r="E3" t="n">
-        <v>2407876.494015553</v>
+        <v>2406993.078328744</v>
       </c>
       <c r="F3" t="n">
-        <v>2208464.289313322</v>
+        <v>2207081.452086482</v>
       </c>
       <c r="G3" t="n">
-        <v>2625551.256005811</v>
+        <v>2628749.357104806</v>
       </c>
       <c r="H3" t="n">
-        <v>106663.9172921882</v>
+        <v>106564.803784021</v>
       </c>
       <c r="I3" t="n">
         <v>10000</v>
@@ -562,19 +562,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5816510245563.147</v>
+        <v>5819592615716.861</v>
       </c>
       <c r="E4" t="n">
-        <v>5797869210443.75</v>
+        <v>5793615679230.234</v>
       </c>
       <c r="F4" t="n">
-        <v>4877314521121.521</v>
+        <v>4871208546166.829</v>
       </c>
       <c r="G4" t="n">
-        <v>6893519397936.982</v>
+        <v>6910323187734.372</v>
       </c>
       <c r="H4" t="n">
-        <v>515448842148.8301</v>
+        <v>515361961336.395</v>
       </c>
       <c r="I4" t="n">
         <v>10000</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39.1994552140211</v>
+        <v>39.19902975165142</v>
       </c>
       <c r="E5" t="n">
-        <v>39.198</v>
+        <v>39.1992989983972</v>
       </c>
       <c r="F5" t="n">
-        <v>38.55996396396397</v>
+        <v>38.54108011022044</v>
       </c>
       <c r="G5" t="n">
-        <v>39.86102154654655</v>
+        <v>39.86288447766403</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3307669276375857</v>
+        <v>0.3373482355480265</v>
       </c>
       <c r="I5" t="n">
         <v>10000</v>
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.50348714357215</v>
+        <v>10.50805661770766</v>
       </c>
       <c r="E6" t="n">
-        <v>10.4606527390551</v>
+        <v>10.47106318143617</v>
       </c>
       <c r="F6" t="n">
-        <v>9.540512225024234</v>
+        <v>9.540976173976034</v>
       </c>
       <c r="G6" t="n">
-        <v>11.68265774654811</v>
+        <v>11.70614729285794</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5556715796279438</v>
+        <v>0.5591076071445559</v>
       </c>
       <c r="I6" t="n">
         <v>10000</v>
@@ -667,19 +667,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>110.6319822025012</v>
+        <v>110.731823937185</v>
       </c>
       <c r="E7" t="n">
-        <v>109.4252557271011</v>
+        <v>109.6431641501221</v>
       </c>
       <c r="F7" t="n">
-        <v>91.02137353453624</v>
+        <v>91.03022636747993</v>
       </c>
       <c r="G7" t="n">
-        <v>136.4844920232444</v>
+        <v>137.0338844453672</v>
       </c>
       <c r="H7" t="n">
-        <v>11.80833425970018</v>
+        <v>11.8756750673703</v>
       </c>
       <c r="I7" t="n">
         <v>10000</v>
@@ -702,19 +702,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.390077608333333</v>
+        <v>2.389554116666667</v>
       </c>
       <c r="E8" t="n">
-        <v>2.38615</v>
+        <v>2.386566666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>2.228347083333333</v>
+        <v>2.228899166666666</v>
       </c>
       <c r="G8" t="n">
-        <v>2.568792083333333</v>
+        <v>2.569304166666667</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08700812673791899</v>
+        <v>0.08626688114075676</v>
       </c>
       <c r="I8" t="n">
         <v>10000</v>
@@ -737,19 +737,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.701904861914793</v>
+        <v>2.702228269377003</v>
       </c>
       <c r="E9" t="n">
-        <v>2.699894127931348</v>
+        <v>2.702228340731376</v>
       </c>
       <c r="F9" t="n">
-        <v>1.979445436949257</v>
+        <v>1.993490338439898</v>
       </c>
       <c r="G9" t="n">
-        <v>3.425044635569411</v>
+        <v>3.418931739663488</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3691605681049299</v>
+        <v>0.3652742980958475</v>
       </c>
       <c r="I9" t="n">
         <v>10000</v>
@@ -772,19 +772,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.436555779929846</v>
+        <v>7.435449590138361</v>
       </c>
       <c r="E10" t="n">
-        <v>7.289428302608163</v>
+        <v>7.302038007312868</v>
       </c>
       <c r="F10" t="n">
-        <v>3.918204250083418</v>
+        <v>3.974003730167668</v>
       </c>
       <c r="G10" t="n">
-        <v>11.73093077546991</v>
+        <v>11.68909424158186</v>
       </c>
       <c r="H10" t="n">
-        <v>2.006521436022852</v>
+        <v>1.988238272374096</v>
       </c>
       <c r="I10" t="n">
         <v>10000</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5841364999999999</v>
+        <v>0.5838205999999999</v>
       </c>
       <c r="E11" t="n">
         <v>0.584</v>
@@ -819,7 +819,7 @@
         <v>0.614</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0157070474273139</v>
+        <v>0.01549041028898499</v>
       </c>
       <c r="I11" t="n">
         <v>10000</v>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.4148713</v>
+        <v>0.4151937</v>
       </c>
       <c r="E12" t="n">
         <v>0.415</v>
       </c>
       <c r="F12" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="G12" t="n">
         <v>0.445</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0156880383657351</v>
+        <v>0.01548386758292425</v>
       </c>
       <c r="I12" t="n">
         <v>10000</v>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.001574670687192552</v>
+        <v>0.001577877381142992</v>
       </c>
       <c r="E13" t="n">
         <v>0.001000000000000112</v>
@@ -889,7 +889,7 @@
         <v>0.004000000000000004</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0008061388908724783</v>
+        <v>0.0008097886820559704</v>
       </c>
       <c r="I13" t="n">
         <v>10000</v>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.7050695999999999</v>
+        <v>0.7049666999999999</v>
       </c>
       <c r="E14" t="n">
         <v>0.705</v>
@@ -924,7 +924,7 @@
         <v>0.733</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0144210385366397</v>
+        <v>0.01434236945090128</v>
       </c>
       <c r="I14" t="n">
         <v>10000</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.2949304</v>
+        <v>0.2950333000000001</v>
       </c>
       <c r="E15" t="n">
         <v>0.295</v>
@@ -959,7 +959,7 @@
         <v>0.323</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0144210385366397</v>
+        <v>0.01434236945090128</v>
       </c>
       <c r="I15" t="n">
         <v>10000</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.6159281</v>
+        <v>0.6163351999999999</v>
       </c>
       <c r="E16" t="n">
         <v>0.616</v>
       </c>
       <c r="F16" t="n">
-        <v>0.585</v>
+        <v>0.586</v>
       </c>
       <c r="G16" t="n">
         <v>0.646</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01548489291473656</v>
+        <v>0.01532590386544721</v>
       </c>
       <c r="I16" t="n">
         <v>10000</v>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.3840719</v>
+        <v>0.3836648</v>
       </c>
       <c r="E17" t="n">
         <v>0.384</v>
@@ -1026,10 +1026,10 @@
         <v>0.354</v>
       </c>
       <c r="G17" t="n">
-        <v>0.415</v>
+        <v>0.414</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01548489291473656</v>
+        <v>0.01532590386544721</v>
       </c>
       <c r="I17" t="n">
         <v>10000</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1719176</v>
+        <v>0.1721087</v>
       </c>
       <c r="E18" t="n">
         <v>0.172</v>
@@ -1064,7 +1064,7 @@
         <v>0.196</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01191915336178229</v>
+        <v>0.01199496028410356</v>
       </c>
       <c r="I18" t="n">
         <v>10000</v>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.3769779402506072</v>
+        <v>0.3771400585221111</v>
       </c>
       <c r="E19" t="n">
         <v>0.3773804446443933</v>
@@ -1099,7 +1099,7 @@
         <v>0.3969685126052191</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01036967296598013</v>
+        <v>0.01043157896593772</v>
       </c>
       <c r="I19" t="n">
         <v>10000</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1422198868</v>
+        <v>0.1423434307</v>
       </c>
       <c r="E20" t="n">
         <v>0.142416</v>
@@ -1134,7 +1134,7 @@
         <v>0.157584</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00780959891717305</v>
+        <v>0.007857164022536708</v>
       </c>
       <c r="I20" t="n">
         <v>10000</v>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.5538021000000001</v>
+        <v>0.5539386000000002</v>
       </c>
       <c r="E21" t="n">
         <v>0.554</v>
       </c>
       <c r="F21" t="n">
-        <v>0.524</v>
+        <v>0.523</v>
       </c>
       <c r="G21" t="n">
         <v>0.585</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01557483846302472</v>
+        <v>0.01572008085647821</v>
       </c>
       <c r="I21" t="n">
         <v>10000</v>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.4968498771295231</v>
+        <v>0.4968304561431652</v>
       </c>
       <c r="E22" t="n">
         <v>0.4970754469896899</v>
@@ -1201,10 +1201,10 @@
         <v>0.4927220311697053</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4994236678412428</v>
+        <v>0.4994707198625361</v>
       </c>
       <c r="H22" t="n">
-        <v>0.001727019003153231</v>
+        <v>0.00174050323456056</v>
       </c>
       <c r="I22" t="n">
         <v>10000</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.2468627827</v>
+        <v>0.2468435312</v>
       </c>
       <c r="E23" t="n">
         <v>0.247084</v>
@@ -1236,10 +1236,10 @@
         <v>0.242775</v>
       </c>
       <c r="G23" t="n">
-        <v>0.249424</v>
+        <v>0.249471</v>
       </c>
       <c r="H23" t="n">
-        <v>0.001713562876597735</v>
+        <v>0.001726887380065328</v>
       </c>
       <c r="I23" t="n">
         <v>10000</v>
